--- a/summed_ages.xlsx
+++ b/summed_ages.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amcclary\Documents\GitHub\Demographics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3810891B-9C27-4A0E-AE05-FFE3BD15C80D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51202F0B-06CD-4B9A-B3A0-7C45A9B0C3DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="525" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Age_2022" sheetId="1" r:id="rId1"/>
@@ -546,6 +546,7 @@
   <cols>
     <col min="1" max="1" width="100.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
